--- a/data/employees/EMP045/AST-EMP045-06.xlsx
+++ b/data/employees/EMP045/AST-EMP045-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor Comparison - Casey Lee (Procurement)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Casey Lee | Role: Senior Engineer | Location: Hsinchu | Date: 2025-02-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>On-Time %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Quality %</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Spend YTD ($K)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>85</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acme Components</t>
+          <t>EMP045</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>97</v>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>99</v>
       </c>
-      <c r="F5" t="n">
-        <v>1450</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GlobalParts Inc</t>
+          <t>EMP045</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mechanical</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91</v>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" t="n">
-        <v>820</v>
+        <v>72</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TechSupply Co</t>
+          <t>EMP045</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>99</v>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2100</v>
+        <v>61</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CleanRoom Solutions</t>
+          <t>EMP045</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumables</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88</v>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E8" t="n">
         <v>95</v>
       </c>
-      <c r="F8" t="n">
-        <v>340</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>67</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>96</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>72</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>85</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>79</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>94</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>99</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>91</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>92</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>89</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>97</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>89</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>89</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>97</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>89</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp045 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>71</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP045</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP045 contributes to ast emp045 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>